--- a/human_resources_forms/008_job_opportunity_questionnaire--human_resources_forms.xlsx
+++ b/human_resources_forms/008_job_opportunity_questionnaire--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -811,8 +811,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,12 +840,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'internship'}</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Internship'}</t>
+          <t>Internship</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'customer_service'}</t>
+          <t>customer_service</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Customer Service'}</t>
+          <t>Customer Service</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'software_development'}</t>
+          <t>software_development</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Software Development'}</t>
+          <t>Software Development</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'entry_level'}</t>
+          <t>entry_level</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Entry Level'}</t>
+          <t>Entry Level</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'mid-level'}</t>
+          <t>mid-level</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Mid-level'}</t>
+          <t>Mid-level</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
